--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487403_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487403_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.6163</v>
+        <v>8.6922</v>
       </c>
       <c r="E2" t="n">
-        <v>8.950100000000001</v>
+        <v>7.5338</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6663</v>
+        <v>1.1584</v>
       </c>
       <c r="G2" t="n">
         <v>7.8371</v>
@@ -610,13 +610,13 @@
         <v>2.546</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5496</v>
+        <v>1.6255</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6566</v>
+        <v>1.2404</v>
       </c>
       <c r="U2" t="n">
-        <v>0.893</v>
+        <v>0.3851</v>
       </c>
       <c r="V2" t="n">
         <v>-2.3371</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6519</v>
+        <v>6.0243</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9794</v>
+        <v>3.138</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6724</v>
+        <v>2.8863</v>
       </c>
       <c r="G3" t="n">
         <v>4.6173</v>
@@ -688,13 +688,13 @@
         <v>1.9585</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8895999999999999</v>
+        <v>0.4829</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6181</v>
+        <v>0.5405</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2715</v>
+        <v>-0.0576</v>
       </c>
       <c r="V3" t="n">
         <v>-0.0551</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3069</v>
+        <v>2.9538</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6803</v>
+        <v>-0.0333</v>
       </c>
       <c r="F4" t="n">
         <v>2.9871</v>
@@ -766,10 +766,10 @@
         <v>2.1543</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0482</v>
+        <v>0.6952</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0047</v>
+        <v>0.6516</v>
       </c>
       <c r="U4" t="n">
         <v>0.0435</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1206</v>
+        <v>1.8489</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2146</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3352</v>
+        <v>1.2283</v>
       </c>
       <c r="G5" t="n">
         <v>0.4597</v>
@@ -844,13 +844,13 @@
         <v>1.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.097</v>
+        <v>-0.3688</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5587</v>
+        <v>0.2764</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5383</v>
+        <v>-0.6452</v>
       </c>
       <c r="V5" t="n">
         <v>3.7164</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9439</v>
+        <v>0.699</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.5643</v>
+        <v>-1.4884</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5082</v>
+        <v>2.1874</v>
       </c>
       <c r="G6" t="n">
         <v>2.6516</v>
@@ -922,13 +922,13 @@
         <v>1.5668</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8346</v>
+        <v>1.5897</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0016</v>
+        <v>1.0775</v>
       </c>
       <c r="U6" t="n">
-        <v>0.833</v>
+        <v>0.5123</v>
       </c>
       <c r="V6" t="n">
         <v>-0.9963</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.5535</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7027</v>
+        <v>0.3956</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1044</v>
+        <v>0.1578</v>
       </c>
       <c r="G7" t="n">
         <v>0.0892</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7179</v>
+        <v>0.4643</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6822</v>
+        <v>0.3752</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0356</v>
+        <v>0.0891</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0736</v>
+        <v>-0.6551</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2669</v>
+        <v>-2.0622</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1933</v>
+        <v>1.4071</v>
       </c>
       <c r="G8" t="n">
         <v>0.2761</v>
@@ -1078,13 +1078,13 @@
         <v>0.7834</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6826</v>
+        <v>-0.2641</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3388</v>
+        <v>-0.1341</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3438</v>
+        <v>-0.13</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2754</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. SANJURJO BOTEJARA</t>
+          <t>A. AÑON DOSIL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.617</v>
+        <v>-1.5064</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3471</v>
+        <v>-3.5049</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7301</v>
+        <v>1.9985</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4537</v>
+        <v>4.0762</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.9654</v>
+        <v>0.0892</v>
       </c>
       <c r="I9" t="n">
-        <v>2.5117</v>
+        <v>3.987</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.8994</v>
+        <v>1.8024</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.6269</v>
+        <v>1.1058</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7275</v>
+        <v>0.6967</v>
       </c>
       <c r="M9" t="n">
-        <v>1.4457</v>
+        <v>2.2737</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3385</v>
+        <v>-1.0166</v>
       </c>
       <c r="O9" t="n">
-        <v>1.7842</v>
+        <v>3.2903</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3917</v>
+        <v>-3.7211</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1751</v>
+        <v>-6.0713</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7834</v>
+        <v>2.3502</v>
       </c>
       <c r="S9" t="n">
-        <v>0.445</v>
+        <v>0.0185</v>
       </c>
       <c r="T9" t="n">
-        <v>1.3933</v>
+        <v>0.764</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9483</v>
+        <v>-0.7455000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2166</v>
+        <v>-1.88</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6659</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5507</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. AÑON DOSIL</t>
+          <t>P. SANJURJO BOTEJARA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8775</v>
+        <v>-2.6299</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.5018</v>
+        <v>-3.4134</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6242</v>
+        <v>0.7835</v>
       </c>
       <c r="G10" t="n">
-        <v>4.0762</v>
+        <v>-0.4537</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0892</v>
+        <v>-2.9654</v>
       </c>
       <c r="I10" t="n">
-        <v>3.987</v>
+        <v>2.5117</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8024</v>
+        <v>-1.8994</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1058</v>
+        <v>-2.6269</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6967</v>
+        <v>0.7275</v>
       </c>
       <c r="M10" t="n">
-        <v>2.2737</v>
+        <v>1.4457</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0166</v>
+        <v>-0.3385</v>
       </c>
       <c r="O10" t="n">
-        <v>3.2903</v>
+        <v>1.7842</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.7211</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q10" t="n">
-        <v>-6.0713</v>
+        <v>-1.1751</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3502</v>
+        <v>0.7834</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3526</v>
+        <v>-0.5678</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2329</v>
+        <v>0.327</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1197</v>
+        <v>-0.8948</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.88</v>
+        <v>-1.2166</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.88</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.0265</v>
+        <v>-5.9403</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.473</v>
+        <v>-3.4136</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.5535</v>
+        <v>-2.5267</v>
       </c>
       <c r="G11" t="n">
         <v>-1.7028</v>
@@ -1312,13 +1312,13 @@
         <v>0.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0769</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.1541</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1716</v>
+        <v>-0.1448</v>
       </c>
       <c r="V11" t="n">
         <v>-1.7007</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.852000000000004</v>
+        <v>10.04</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4158</v>
+        <v>-2.2279</v>
       </c>
       <c r="F12" t="n">
         <v>12.2677</v>
@@ -1390,19 +1390,19 @@
         <v>13.7094</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4966</v>
+        <v>3.6847</v>
       </c>
       <c r="T12" t="n">
-        <v>4.0846</v>
+        <v>5.272599999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.5881</v>
+        <v>-1.5879</v>
       </c>
       <c r="V12" t="n">
         <v>-2.2155</v>
       </c>
       <c r="W12" t="n">
-        <v>6.6788</v>
+        <v>6.678800000000001</v>
       </c>
       <c r="X12" t="n">
         <v>-8.894299999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.4736</v>
+        <v>5.4794</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8752</v>
+        <v>4.2846</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5984</v>
+        <v>1.1949</v>
       </c>
       <c r="G13" t="n">
         <v>1.3352</v>
@@ -1468,13 +1468,13 @@
         <v>3.7211</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.7038</v>
+        <v>-0.698</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5893</v>
+        <v>-0.18</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1145</v>
+        <v>-0.518</v>
       </c>
       <c r="V13" t="n">
         <v>2.1003</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.286</v>
+        <v>2.9388</v>
       </c>
       <c r="E14" t="n">
-        <v>0.743</v>
+        <v>1.1524</v>
       </c>
       <c r="F14" t="n">
-        <v>1.543</v>
+        <v>1.7864</v>
       </c>
       <c r="G14" t="n">
         <v>1.2172</v>
@@ -1546,13 +1546,13 @@
         <v>0.9792</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2434</v>
+        <v>0.4093</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1253</v>
+        <v>0.2841</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1181</v>
+        <v>0.1253</v>
       </c>
       <c r="V14" t="n">
         <v>0.3329</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8783</v>
+        <v>2.6868</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1354</v>
+        <v>0.647</v>
       </c>
       <c r="F15" t="n">
-        <v>1.743</v>
+        <v>2.0398</v>
       </c>
       <c r="G15" t="n">
         <v>0.5999</v>
@@ -1624,13 +1624,13 @@
         <v>2.1543</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7423</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3276</v>
+        <v>0.1841</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4148</v>
+        <v>-0.1179</v>
       </c>
       <c r="V15" t="n">
         <v>1.8249</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.641</v>
+        <v>0.6711</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1055</v>
+        <v>-0.3272</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5355</v>
+        <v>0.9983</v>
       </c>
       <c r="G16" t="n">
         <v>-2.4527</v>
@@ -1702,13 +1702,13 @@
         <v>2.7419</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3519</v>
+        <v>0.382</v>
       </c>
       <c r="T16" t="n">
-        <v>2.0691</v>
+        <v>0.6364</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7171999999999999</v>
+        <v>-0.2544</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2213</v>
+        <v>0.4296</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4624</v>
+        <v>0.9741</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6837</v>
+        <v>-0.5444</v>
       </c>
       <c r="G17" t="n">
         <v>1.2938</v>
@@ -1780,13 +1780,13 @@
         <v>2.1543</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0473</v>
+        <v>0.6036</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2358</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2832</v>
+        <v>-0.1439</v>
       </c>
       <c r="V17" t="n">
         <v>1.2742</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.982</v>
+        <v>-0.853</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3764</v>
+        <v>-1.274</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3943</v>
+        <v>0.4211</v>
       </c>
       <c r="G18" t="n">
         <v>-2.4036</v>
@@ -1858,13 +1858,13 @@
         <v>1.9585</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2615</v>
+        <v>-0.1325</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0223</v>
+        <v>0.1247</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2839</v>
+        <v>-0.2572</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2754</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9498</v>
+        <v>-1.8963</v>
       </c>
       <c r="E19" t="n">
         <v>-2.0127</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0629</v>
+        <v>0.1163</v>
       </c>
       <c r="G19" t="n">
         <v>-1.4926</v>
@@ -1936,13 +1936,13 @@
         <v>0.7834</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2406</v>
+        <v>-1.1872</v>
       </c>
       <c r="T19" t="n">
         <v>-0.6534</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.5337</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1674</v>
+        <v>-3.6839</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.0238</v>
+        <v>-4.2518</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8563</v>
+        <v>0.5679</v>
       </c>
       <c r="G20" t="n">
         <v>-4.8674</v>
@@ -2014,13 +2014,13 @@
         <v>3.5253</v>
       </c>
       <c r="S20" t="n">
-        <v>2.1124</v>
+        <v>0.5959</v>
       </c>
       <c r="T20" t="n">
-        <v>1.8908</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2216</v>
+        <v>-0.0669</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.6991</v>
+        <v>-4.4649</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.6348</v>
+        <v>-4.4302</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0643</v>
+        <v>-0.0348</v>
       </c>
       <c r="G21" t="n">
         <v>-4.9771</v>
@@ -2092,13 +2092,13 @@
         <v>2.7419</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1517</v>
+        <v>-0.9175</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.111</v>
+        <v>-0.9063</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0407</v>
+        <v>-0.0112</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3329</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-9.1114</v>
+        <v>-8.113</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.5417</v>
+        <v>-7.0301</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5696</v>
+        <v>-1.0829</v>
       </c>
       <c r="G22" t="n">
         <v>-6.6159</v>
@@ -2170,13 +2170,13 @@
         <v>2.7419</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5703</v>
+        <v>0.4282</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1764</v>
+        <v>0.6881</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7467</v>
+        <v>-0.26</v>
       </c>
       <c r="V22" t="n">
         <v>-2.7086</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.8521</v>
+        <v>-6.8054</v>
       </c>
       <c r="E23" t="n">
         <v>-12.2679</v>
       </c>
       <c r="F23" t="n">
-        <v>3.415799999999999</v>
+        <v>5.4626</v>
       </c>
       <c r="G23" t="n">
         <v>-18.3632</v>
@@ -2248,13 +2248,13 @@
         <v>23.5018</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.4966</v>
+        <v>-0.45</v>
       </c>
       <c r="T23" t="n">
-        <v>1.5878</v>
+        <v>1.588</v>
       </c>
       <c r="U23" t="n">
-        <v>-4.084700000000001</v>
+        <v>-2.0379</v>
       </c>
       <c r="V23" t="n">
         <v>2.215399999999999</v>
